--- a/Hoadon/HDVao/11/3502386218_HDDienTuMayTinhTien.xlsx
+++ b/Hoadon/HDVao/11/3502386218_HDDienTuMayTinhTien.xlsx
@@ -1043,32 +1043,32 @@
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>C25MTT</t>
+          <t>C25MEX</t>
         </is>
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>4386</t>
+          <t>46790</t>
         </is>
       </c>
       <c r="E17" s="7" t="inlineStr">
         <is>
-          <t>10/11/2025</t>
+          <t>19/11/2025</t>
         </is>
       </c>
       <c r="F17" s="7" t="inlineStr">
         <is>
-          <t>0317887567</t>
+          <t>0304132047</t>
         </is>
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN SEPAY</t>
+          <t>Công ty cổ phần phát hành sách TPHCM - Fahasa</t>
         </is>
       </c>
       <c r="H17" s="6" t="inlineStr">
         <is>
-          <t>Số 13, Đường Số 38, Khu Đô Thị Vạn Phúc City, Phường Hiệp Bình, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>60-62 Lê Lợi, Phường Sài Gòn, TP. Hồ Chí Minh</t>
         </is>
       </c>
       <c r="I17" s="7" t="inlineStr">
@@ -1078,12 +1078,12 @@
       </c>
       <c r="J17" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIET NAM</t>
         </is>
       </c>
       <c r="K17" s="6"/>
       <c r="L17" s="13" t="n">
-        <v>5712000.0</v>
+        <v>735000.0</v>
       </c>
       <c r="M17" s="13" t="n">
         <v>0.0</v>
@@ -1092,7 +1092,7 @@
         <v>0.0</v>
       </c>
       <c r="O17" s="13" t="n">
-        <v>5712000.0</v>
+        <v>735000.0</v>
       </c>
       <c r="P17" s="6" t="inlineStr">
         <is>
@@ -1116,32 +1116,32 @@
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>C25MDO</t>
+          <t>C25MEX</t>
         </is>
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>260059</t>
+          <t>46791</t>
         </is>
       </c>
       <c r="E18" s="7" t="inlineStr">
         <is>
-          <t>01/11/2025</t>
+          <t>19/11/2025</t>
         </is>
       </c>
       <c r="F18" s="7" t="inlineStr">
         <is>
-          <t>3502397072</t>
+          <t>0304132047</t>
         </is>
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH XĂNG DẦU VŨNG TÀU</t>
+          <t>Công ty cổ phần phát hành sách TPHCM - Fahasa</t>
         </is>
       </c>
       <c r="H18" s="6" t="inlineStr">
         <is>
-          <t>Số 510 Cách Mạng Tháng Tám, Phường Bà Rịa, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>60-62 Lê Lợi, Phường Sài Gòn, TP. Hồ Chí Minh</t>
         </is>
       </c>
       <c r="I18" s="7" t="inlineStr">
@@ -1151,21 +1151,21 @@
       </c>
       <c r="J18" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIET NAM</t>
         </is>
       </c>
       <c r="K18" s="6"/>
       <c r="L18" s="13" t="n">
-        <v>740741.0</v>
+        <v>735000.0</v>
       </c>
       <c r="M18" s="13" t="n">
-        <v>59259.0</v>
+        <v>0.0</v>
       </c>
       <c r="N18" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O18" s="13" t="n">
-        <v>800000.0</v>
+        <v>735000.0</v>
       </c>
       <c r="P18" s="6" t="inlineStr">
         <is>
@@ -1189,32 +1189,32 @@
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>C25MDO</t>
+          <t>C25MEX</t>
         </is>
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>264157</t>
+          <t>46792</t>
         </is>
       </c>
       <c r="E19" s="7" t="inlineStr">
         <is>
-          <t>04/11/2025</t>
+          <t>19/11/2025</t>
         </is>
       </c>
       <c r="F19" s="7" t="inlineStr">
         <is>
-          <t>3502397072</t>
+          <t>0304132047</t>
         </is>
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH XĂNG DẦU VŨNG TÀU</t>
+          <t>Công ty cổ phần phát hành sách TPHCM - Fahasa</t>
         </is>
       </c>
       <c r="H19" s="6" t="inlineStr">
         <is>
-          <t>Số 510 Cách Mạng Tháng Tám, Phường Bà Rịa, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>60-62 Lê Lợi, Phường Sài Gòn, TP. Hồ Chí Minh</t>
         </is>
       </c>
       <c r="I19" s="7" t="inlineStr">
@@ -1224,21 +1224,21 @@
       </c>
       <c r="J19" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIET NAM</t>
         </is>
       </c>
       <c r="K19" s="6"/>
       <c r="L19" s="13" t="n">
-        <v>740741.0</v>
+        <v>584500.0</v>
       </c>
       <c r="M19" s="13" t="n">
-        <v>59259.0</v>
+        <v>0.0</v>
       </c>
       <c r="N19" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O19" s="13" t="n">
-        <v>800000.0</v>
+        <v>584500.0</v>
       </c>
       <c r="P19" s="6" t="inlineStr">
         <is>
@@ -1262,32 +1262,32 @@
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>C25MDO</t>
+          <t>C25MEX</t>
         </is>
       </c>
       <c r="D20" s="7" t="inlineStr">
         <is>
-          <t>267298</t>
+          <t>46793</t>
         </is>
       </c>
       <c r="E20" s="7" t="inlineStr">
         <is>
-          <t>07/11/2025</t>
+          <t>19/11/2025</t>
         </is>
       </c>
       <c r="F20" s="7" t="inlineStr">
         <is>
-          <t>3502397072</t>
+          <t>0304132047</t>
         </is>
       </c>
       <c r="G20" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH XĂNG DẦU VŨNG TÀU</t>
+          <t>Công ty cổ phần phát hành sách TPHCM - Fahasa</t>
         </is>
       </c>
       <c r="H20" s="6" t="inlineStr">
         <is>
-          <t>Số 510 Cách Mạng Tháng Tám, Phường Bà Rịa, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>60-62 Lê Lợi, Phường Sài Gòn, TP. Hồ Chí Minh</t>
         </is>
       </c>
       <c r="I20" s="7" t="inlineStr">
@@ -1297,21 +1297,21 @@
       </c>
       <c r="J20" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIET NAM</t>
         </is>
       </c>
       <c r="K20" s="6"/>
       <c r="L20" s="13" t="n">
-        <v>740741.0</v>
+        <v>584500.0</v>
       </c>
       <c r="M20" s="13" t="n">
-        <v>59259.0</v>
+        <v>0.0</v>
       </c>
       <c r="N20" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O20" s="13" t="n">
-        <v>800000.0</v>
+        <v>584500.0</v>
       </c>
       <c r="P20" s="6" t="inlineStr">
         <is>
@@ -1335,32 +1335,32 @@
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>C25MDO</t>
+          <t>C25MEX</t>
         </is>
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t>269619</t>
+          <t>46794</t>
         </is>
       </c>
       <c r="E21" s="7" t="inlineStr">
         <is>
-          <t>10/11/2025</t>
+          <t>19/11/2025</t>
         </is>
       </c>
       <c r="F21" s="7" t="inlineStr">
         <is>
-          <t>3502397072</t>
+          <t>0304132047</t>
         </is>
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH XĂNG DẦU VŨNG TÀU</t>
+          <t>Công ty cổ phần phát hành sách TPHCM - Fahasa</t>
         </is>
       </c>
       <c r="H21" s="6" t="inlineStr">
         <is>
-          <t>Số 510 Cách Mạng Tháng Tám, Phường Bà Rịa, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>60-62 Lê Lợi, Phường Sài Gòn, TP. Hồ Chí Minh</t>
         </is>
       </c>
       <c r="I21" s="7" t="inlineStr">
@@ -1370,21 +1370,21 @@
       </c>
       <c r="J21" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIET NAM</t>
         </is>
       </c>
       <c r="K21" s="6"/>
       <c r="L21" s="13" t="n">
-        <v>462963.0</v>
+        <v>527800.0</v>
       </c>
       <c r="M21" s="13" t="n">
-        <v>37037.0</v>
+        <v>0.0</v>
       </c>
       <c r="N21" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O21" s="13" t="n">
-        <v>500000.0</v>
+        <v>527800.0</v>
       </c>
       <c r="P21" s="6" t="inlineStr">
         <is>
@@ -1408,32 +1408,32 @@
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>C25MDO</t>
+          <t>C25MEX</t>
         </is>
       </c>
       <c r="D22" s="7" t="inlineStr">
         <is>
-          <t>270810</t>
+          <t>46795</t>
         </is>
       </c>
       <c r="E22" s="7" t="inlineStr">
         <is>
-          <t>11/11/2025</t>
+          <t>19/11/2025</t>
         </is>
       </c>
       <c r="F22" s="7" t="inlineStr">
         <is>
-          <t>3502397072</t>
+          <t>0304132047</t>
         </is>
       </c>
       <c r="G22" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH XĂNG DẦU VŨNG TÀU</t>
+          <t>Công ty cổ phần phát hành sách TPHCM - Fahasa</t>
         </is>
       </c>
       <c r="H22" s="6" t="inlineStr">
         <is>
-          <t>Số 510 Cách Mạng Tháng Tám, Phường Bà Rịa, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>60-62 Lê Lợi, Phường Sài Gòn, TP. Hồ Chí Minh</t>
         </is>
       </c>
       <c r="I22" s="7" t="inlineStr">
@@ -1443,21 +1443,21 @@
       </c>
       <c r="J22" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIET NAM</t>
         </is>
       </c>
       <c r="K22" s="6"/>
       <c r="L22" s="13" t="n">
-        <v>740741.0</v>
+        <v>402500.0</v>
       </c>
       <c r="M22" s="13" t="n">
-        <v>59259.0</v>
+        <v>0.0</v>
       </c>
       <c r="N22" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O22" s="13" t="n">
-        <v>800000.0</v>
+        <v>402500.0</v>
       </c>
       <c r="P22" s="6" t="inlineStr">
         <is>
@@ -1481,32 +1481,32 @@
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>C25MDO</t>
+          <t>C25MEX</t>
         </is>
       </c>
       <c r="D23" s="7" t="inlineStr">
         <is>
-          <t>274708</t>
+          <t>46796</t>
         </is>
       </c>
       <c r="E23" s="7" t="inlineStr">
         <is>
-          <t>15/11/2025</t>
+          <t>19/11/2025</t>
         </is>
       </c>
       <c r="F23" s="7" t="inlineStr">
         <is>
-          <t>3502397072</t>
+          <t>0304132047</t>
         </is>
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH XĂNG DẦU VŨNG TÀU</t>
+          <t>Công ty cổ phần phát hành sách TPHCM - Fahasa</t>
         </is>
       </c>
       <c r="H23" s="6" t="inlineStr">
         <is>
-          <t>Số 510 Cách Mạng Tháng Tám, Phường Bà Rịa, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>60-62 Lê Lợi, Phường Sài Gòn, TP. Hồ Chí Minh</t>
         </is>
       </c>
       <c r="I23" s="7" t="inlineStr">
@@ -1516,21 +1516,21 @@
       </c>
       <c r="J23" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIET NAM</t>
         </is>
       </c>
       <c r="K23" s="6"/>
       <c r="L23" s="13" t="n">
-        <v>740741.0</v>
+        <v>493500.0</v>
       </c>
       <c r="M23" s="13" t="n">
-        <v>59259.0</v>
+        <v>0.0</v>
       </c>
       <c r="N23" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O23" s="13" t="n">
-        <v>800000.0</v>
+        <v>493500.0</v>
       </c>
       <c r="P23" s="6" t="inlineStr">
         <is>
@@ -1554,32 +1554,32 @@
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>C25MDO</t>
+          <t>C25MEX</t>
         </is>
       </c>
       <c r="D24" s="7" t="inlineStr">
         <is>
-          <t>278331</t>
+          <t>46797</t>
         </is>
       </c>
       <c r="E24" s="7" t="inlineStr">
         <is>
-          <t>18/11/2025</t>
+          <t>19/11/2025</t>
         </is>
       </c>
       <c r="F24" s="7" t="inlineStr">
         <is>
-          <t>3502397072</t>
+          <t>0304132047</t>
         </is>
       </c>
       <c r="G24" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH XĂNG DẦU VŨNG TÀU</t>
+          <t>Công ty cổ phần phát hành sách TPHCM - Fahasa</t>
         </is>
       </c>
       <c r="H24" s="6" t="inlineStr">
         <is>
-          <t>Số 510 Cách Mạng Tháng Tám, Phường Bà Rịa, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>60-62 Lê Lợi, Phường Sài Gòn, TP. Hồ Chí Minh</t>
         </is>
       </c>
       <c r="I24" s="7" t="inlineStr">
@@ -1589,28 +1589,758 @@
       </c>
       <c r="J24" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIET NAM</t>
         </is>
       </c>
       <c r="K24" s="6"/>
       <c r="L24" s="13" t="n">
+        <v>630000.0</v>
+      </c>
+      <c r="M24" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N24" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O24" s="13" t="n">
+        <v>630000.0</v>
+      </c>
+      <c r="P24" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q24" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="n">
+        <v>19.0</v>
+      </c>
+      <c r="B25" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>C25MEX</t>
+        </is>
+      </c>
+      <c r="D25" s="7" t="inlineStr">
+        <is>
+          <t>46798</t>
+        </is>
+      </c>
+      <c r="E25" s="7" t="inlineStr">
+        <is>
+          <t>19/11/2025</t>
+        </is>
+      </c>
+      <c r="F25" s="7" t="inlineStr">
+        <is>
+          <t>0304132047</t>
+        </is>
+      </c>
+      <c r="G25" s="6" t="inlineStr">
+        <is>
+          <t>Công ty cổ phần phát hành sách TPHCM - Fahasa</t>
+        </is>
+      </c>
+      <c r="H25" s="6" t="inlineStr">
+        <is>
+          <t>60-62 Lê Lợi, Phường Sài Gòn, TP. Hồ Chí Minh</t>
+        </is>
+      </c>
+      <c r="I25" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J25" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIET NAM</t>
+        </is>
+      </c>
+      <c r="K25" s="6"/>
+      <c r="L25" s="13" t="n">
+        <v>126000.0</v>
+      </c>
+      <c r="M25" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N25" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O25" s="13" t="n">
+        <v>126000.0</v>
+      </c>
+      <c r="P25" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q25" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="n">
+        <v>20.0</v>
+      </c>
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="inlineStr">
+        <is>
+          <t>C25MEX</t>
+        </is>
+      </c>
+      <c r="D26" s="7" t="inlineStr">
+        <is>
+          <t>46799</t>
+        </is>
+      </c>
+      <c r="E26" s="7" t="inlineStr">
+        <is>
+          <t>19/11/2025</t>
+        </is>
+      </c>
+      <c r="F26" s="7" t="inlineStr">
+        <is>
+          <t>0304132047</t>
+        </is>
+      </c>
+      <c r="G26" s="6" t="inlineStr">
+        <is>
+          <t>Công ty cổ phần phát hành sách TPHCM - Fahasa</t>
+        </is>
+      </c>
+      <c r="H26" s="6" t="inlineStr">
+        <is>
+          <t>60-62 Lê Lợi, Phường Sài Gòn, TP. Hồ Chí Minh</t>
+        </is>
+      </c>
+      <c r="I26" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J26" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIET NAM</t>
+        </is>
+      </c>
+      <c r="K26" s="6"/>
+      <c r="L26" s="13" t="n">
+        <v>456450.0</v>
+      </c>
+      <c r="M26" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N26" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O26" s="13" t="n">
+        <v>456450.0</v>
+      </c>
+      <c r="P26" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q26" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="n">
+        <v>21.0</v>
+      </c>
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="inlineStr">
+        <is>
+          <t>C25MTT</t>
+        </is>
+      </c>
+      <c r="D27" s="7" t="inlineStr">
+        <is>
+          <t>4386</t>
+        </is>
+      </c>
+      <c r="E27" s="7" t="inlineStr">
+        <is>
+          <t>10/11/2025</t>
+        </is>
+      </c>
+      <c r="F27" s="7" t="inlineStr">
+        <is>
+          <t>0317887567</t>
+        </is>
+      </c>
+      <c r="G27" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN SEPAY</t>
+        </is>
+      </c>
+      <c r="H27" s="6" t="inlineStr">
+        <is>
+          <t>Số 13, Đường Số 38, Khu Đô Thị Vạn Phúc City, Phường Hiệp Bình, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I27" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J27" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="K27" s="6"/>
+      <c r="L27" s="13" t="n">
+        <v>5712000.0</v>
+      </c>
+      <c r="M27" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N27" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O27" s="13" t="n">
+        <v>5712000.0</v>
+      </c>
+      <c r="P27" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q27" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="n">
+        <v>22.0</v>
+      </c>
+      <c r="B28" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="inlineStr">
+        <is>
+          <t>C25MDO</t>
+        </is>
+      </c>
+      <c r="D28" s="7" t="inlineStr">
+        <is>
+          <t>260059</t>
+        </is>
+      </c>
+      <c r="E28" s="7" t="inlineStr">
+        <is>
+          <t>01/11/2025</t>
+        </is>
+      </c>
+      <c r="F28" s="7" t="inlineStr">
+        <is>
+          <t>3502397072</t>
+        </is>
+      </c>
+      <c r="G28" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH XĂNG DẦU VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H28" s="6" t="inlineStr">
+        <is>
+          <t>Số 510 Cách Mạng Tháng Tám, Phường Bà Rịa, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I28" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J28" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="K28" s="6"/>
+      <c r="L28" s="13" t="n">
         <v>740741.0</v>
       </c>
-      <c r="M24" s="13" t="n">
+      <c r="M28" s="13" t="n">
         <v>59259.0</v>
       </c>
-      <c r="N24" s="13" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="O24" s="13" t="n">
+      <c r="N28" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O28" s="13" t="n">
         <v>800000.0</v>
       </c>
-      <c r="P24" s="6" t="inlineStr">
+      <c r="P28" s="6" t="inlineStr">
         <is>
           <t>Hóa đơn mới</t>
         </is>
       </c>
-      <c r="Q24" s="6" t="inlineStr">
+      <c r="Q28" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="n">
+        <v>23.0</v>
+      </c>
+      <c r="B29" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t>C25MDO</t>
+        </is>
+      </c>
+      <c r="D29" s="7" t="inlineStr">
+        <is>
+          <t>264157</t>
+        </is>
+      </c>
+      <c r="E29" s="7" t="inlineStr">
+        <is>
+          <t>04/11/2025</t>
+        </is>
+      </c>
+      <c r="F29" s="7" t="inlineStr">
+        <is>
+          <t>3502397072</t>
+        </is>
+      </c>
+      <c r="G29" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH XĂNG DẦU VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H29" s="6" t="inlineStr">
+        <is>
+          <t>Số 510 Cách Mạng Tháng Tám, Phường Bà Rịa, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I29" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J29" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="K29" s="6"/>
+      <c r="L29" s="13" t="n">
+        <v>740741.0</v>
+      </c>
+      <c r="M29" s="13" t="n">
+        <v>59259.0</v>
+      </c>
+      <c r="N29" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O29" s="13" t="n">
+        <v>800000.0</v>
+      </c>
+      <c r="P29" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q29" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="n">
+        <v>24.0</v>
+      </c>
+      <c r="B30" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C30" s="6" t="inlineStr">
+        <is>
+          <t>C25MDO</t>
+        </is>
+      </c>
+      <c r="D30" s="7" t="inlineStr">
+        <is>
+          <t>267298</t>
+        </is>
+      </c>
+      <c r="E30" s="7" t="inlineStr">
+        <is>
+          <t>07/11/2025</t>
+        </is>
+      </c>
+      <c r="F30" s="7" t="inlineStr">
+        <is>
+          <t>3502397072</t>
+        </is>
+      </c>
+      <c r="G30" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH XĂNG DẦU VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H30" s="6" t="inlineStr">
+        <is>
+          <t>Số 510 Cách Mạng Tháng Tám, Phường Bà Rịa, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I30" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J30" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="K30" s="6"/>
+      <c r="L30" s="13" t="n">
+        <v>740741.0</v>
+      </c>
+      <c r="M30" s="13" t="n">
+        <v>59259.0</v>
+      </c>
+      <c r="N30" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O30" s="13" t="n">
+        <v>800000.0</v>
+      </c>
+      <c r="P30" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q30" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="n">
+        <v>25.0</v>
+      </c>
+      <c r="B31" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C31" s="6" t="inlineStr">
+        <is>
+          <t>C25MDO</t>
+        </is>
+      </c>
+      <c r="D31" s="7" t="inlineStr">
+        <is>
+          <t>269619</t>
+        </is>
+      </c>
+      <c r="E31" s="7" t="inlineStr">
+        <is>
+          <t>10/11/2025</t>
+        </is>
+      </c>
+      <c r="F31" s="7" t="inlineStr">
+        <is>
+          <t>3502397072</t>
+        </is>
+      </c>
+      <c r="G31" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH XĂNG DẦU VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H31" s="6" t="inlineStr">
+        <is>
+          <t>Số 510 Cách Mạng Tháng Tám, Phường Bà Rịa, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I31" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J31" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="K31" s="6"/>
+      <c r="L31" s="13" t="n">
+        <v>462963.0</v>
+      </c>
+      <c r="M31" s="13" t="n">
+        <v>37037.0</v>
+      </c>
+      <c r="N31" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O31" s="13" t="n">
+        <v>500000.0</v>
+      </c>
+      <c r="P31" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q31" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="n">
+        <v>26.0</v>
+      </c>
+      <c r="B32" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C32" s="6" t="inlineStr">
+        <is>
+          <t>C25MDO</t>
+        </is>
+      </c>
+      <c r="D32" s="7" t="inlineStr">
+        <is>
+          <t>270810</t>
+        </is>
+      </c>
+      <c r="E32" s="7" t="inlineStr">
+        <is>
+          <t>11/11/2025</t>
+        </is>
+      </c>
+      <c r="F32" s="7" t="inlineStr">
+        <is>
+          <t>3502397072</t>
+        </is>
+      </c>
+      <c r="G32" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH XĂNG DẦU VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H32" s="6" t="inlineStr">
+        <is>
+          <t>Số 510 Cách Mạng Tháng Tám, Phường Bà Rịa, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I32" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J32" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="K32" s="6"/>
+      <c r="L32" s="13" t="n">
+        <v>740741.0</v>
+      </c>
+      <c r="M32" s="13" t="n">
+        <v>59259.0</v>
+      </c>
+      <c r="N32" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O32" s="13" t="n">
+        <v>800000.0</v>
+      </c>
+      <c r="P32" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q32" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="n">
+        <v>27.0</v>
+      </c>
+      <c r="B33" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C33" s="6" t="inlineStr">
+        <is>
+          <t>C25MDO</t>
+        </is>
+      </c>
+      <c r="D33" s="7" t="inlineStr">
+        <is>
+          <t>274708</t>
+        </is>
+      </c>
+      <c r="E33" s="7" t="inlineStr">
+        <is>
+          <t>15/11/2025</t>
+        </is>
+      </c>
+      <c r="F33" s="7" t="inlineStr">
+        <is>
+          <t>3502397072</t>
+        </is>
+      </c>
+      <c r="G33" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH XĂNG DẦU VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H33" s="6" t="inlineStr">
+        <is>
+          <t>Số 510 Cách Mạng Tháng Tám, Phường Bà Rịa, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I33" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J33" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="K33" s="6"/>
+      <c r="L33" s="13" t="n">
+        <v>740741.0</v>
+      </c>
+      <c r="M33" s="13" t="n">
+        <v>59259.0</v>
+      </c>
+      <c r="N33" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O33" s="13" t="n">
+        <v>800000.0</v>
+      </c>
+      <c r="P33" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q33" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="n">
+        <v>28.0</v>
+      </c>
+      <c r="B34" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C34" s="6" t="inlineStr">
+        <is>
+          <t>C25MDO</t>
+        </is>
+      </c>
+      <c r="D34" s="7" t="inlineStr">
+        <is>
+          <t>278331</t>
+        </is>
+      </c>
+      <c r="E34" s="7" t="inlineStr">
+        <is>
+          <t>18/11/2025</t>
+        </is>
+      </c>
+      <c r="F34" s="7" t="inlineStr">
+        <is>
+          <t>3502397072</t>
+        </is>
+      </c>
+      <c r="G34" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH XĂNG DẦU VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H34" s="6" t="inlineStr">
+        <is>
+          <t>Số 510 Cách Mạng Tháng Tám, Phường Bà Rịa, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I34" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J34" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="K34" s="6"/>
+      <c r="L34" s="13" t="n">
+        <v>740741.0</v>
+      </c>
+      <c r="M34" s="13" t="n">
+        <v>59259.0</v>
+      </c>
+      <c r="N34" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O34" s="13" t="n">
+        <v>800000.0</v>
+      </c>
+      <c r="P34" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q34" s="6" t="inlineStr">
         <is>
           <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
         </is>

--- a/Hoadon/HDVao/11/3502386218_HDDienTuMayTinhTien.xlsx
+++ b/Hoadon/HDVao/11/3502386218_HDDienTuMayTinhTien.xlsx
@@ -1773,32 +1773,32 @@
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>C25MTT</t>
+          <t>C25MEX</t>
         </is>
       </c>
       <c r="D27" s="7" t="inlineStr">
         <is>
-          <t>4386</t>
+          <t>47320</t>
         </is>
       </c>
       <c r="E27" s="7" t="inlineStr">
         <is>
-          <t>10/11/2025</t>
+          <t>21/11/2025</t>
         </is>
       </c>
       <c r="F27" s="7" t="inlineStr">
         <is>
-          <t>0317887567</t>
+          <t>0304132047</t>
         </is>
       </c>
       <c r="G27" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN SEPAY</t>
+          <t>Công ty cổ phần phát hành sách TPHCM - Fahasa</t>
         </is>
       </c>
       <c r="H27" s="6" t="inlineStr">
         <is>
-          <t>Số 13, Đường Số 38, Khu Đô Thị Vạn Phúc City, Phường Hiệp Bình, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>60-62 Lê Lợi, Phường Sài Gòn, TP. Hồ Chí Minh</t>
         </is>
       </c>
       <c r="I27" s="7" t="inlineStr">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="J27" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIET NAM</t>
         </is>
       </c>
       <c r="K27" s="6"/>
       <c r="L27" s="13" t="n">
-        <v>5712000.0</v>
+        <v>152150.0</v>
       </c>
       <c r="M27" s="13" t="n">
         <v>0.0</v>
@@ -1822,7 +1822,7 @@
         <v>0.0</v>
       </c>
       <c r="O27" s="13" t="n">
-        <v>5712000.0</v>
+        <v>152150.0</v>
       </c>
       <c r="P27" s="6" t="inlineStr">
         <is>
@@ -1846,32 +1846,32 @@
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>C25MDO</t>
+          <t>C25MEX</t>
         </is>
       </c>
       <c r="D28" s="7" t="inlineStr">
         <is>
-          <t>260059</t>
+          <t>48248</t>
         </is>
       </c>
       <c r="E28" s="7" t="inlineStr">
         <is>
-          <t>01/11/2025</t>
+          <t>24/11/2025</t>
         </is>
       </c>
       <c r="F28" s="7" t="inlineStr">
         <is>
-          <t>3502397072</t>
+          <t>0304132047</t>
         </is>
       </c>
       <c r="G28" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH XĂNG DẦU VŨNG TÀU</t>
+          <t>Công ty cổ phần phát hành sách TPHCM - Fahasa</t>
         </is>
       </c>
       <c r="H28" s="6" t="inlineStr">
         <is>
-          <t>Số 510 Cách Mạng Tháng Tám, Phường Bà Rịa, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>60-62 Lê Lợi, Phường Sài Gòn, TP. Hồ Chí Minh</t>
         </is>
       </c>
       <c r="I28" s="7" t="inlineStr">
@@ -1881,21 +1881,21 @@
       </c>
       <c r="J28" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIET NAM</t>
         </is>
       </c>
       <c r="K28" s="6"/>
       <c r="L28" s="13" t="n">
-        <v>740741.0</v>
+        <v>5038080.0</v>
       </c>
       <c r="M28" s="13" t="n">
-        <v>59259.0</v>
+        <v>0.0</v>
       </c>
       <c r="N28" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O28" s="13" t="n">
-        <v>800000.0</v>
+        <v>5038080.0</v>
       </c>
       <c r="P28" s="6" t="inlineStr">
         <is>
@@ -1919,32 +1919,32 @@
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>C25MDO</t>
+          <t>C25MTT</t>
         </is>
       </c>
       <c r="D29" s="7" t="inlineStr">
         <is>
-          <t>264157</t>
+          <t>4386</t>
         </is>
       </c>
       <c r="E29" s="7" t="inlineStr">
         <is>
-          <t>04/11/2025</t>
+          <t>10/11/2025</t>
         </is>
       </c>
       <c r="F29" s="7" t="inlineStr">
         <is>
-          <t>3502397072</t>
+          <t>0317887567</t>
         </is>
       </c>
       <c r="G29" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH XĂNG DẦU VŨNG TÀU</t>
+          <t>CÔNG TY CỔ PHẦN SEPAY</t>
         </is>
       </c>
       <c r="H29" s="6" t="inlineStr">
         <is>
-          <t>Số 510 Cách Mạng Tháng Tám, Phường Bà Rịa, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>Số 13, Đường Số 38, Khu Đô Thị Vạn Phúc City, Phường Hiệp Bình, Thành phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I29" s="7" t="inlineStr">
@@ -1959,16 +1959,16 @@
       </c>
       <c r="K29" s="6"/>
       <c r="L29" s="13" t="n">
-        <v>740741.0</v>
+        <v>5712000.0</v>
       </c>
       <c r="M29" s="13" t="n">
-        <v>59259.0</v>
+        <v>0.0</v>
       </c>
       <c r="N29" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O29" s="13" t="n">
-        <v>800000.0</v>
+        <v>5712000.0</v>
       </c>
       <c r="P29" s="6" t="inlineStr">
         <is>
@@ -1997,12 +1997,12 @@
       </c>
       <c r="D30" s="7" t="inlineStr">
         <is>
-          <t>267298</t>
+          <t>260059</t>
         </is>
       </c>
       <c r="E30" s="7" t="inlineStr">
         <is>
-          <t>07/11/2025</t>
+          <t>01/11/2025</t>
         </is>
       </c>
       <c r="F30" s="7" t="inlineStr">
@@ -2070,12 +2070,12 @@
       </c>
       <c r="D31" s="7" t="inlineStr">
         <is>
-          <t>269619</t>
+          <t>264157</t>
         </is>
       </c>
       <c r="E31" s="7" t="inlineStr">
         <is>
-          <t>10/11/2025</t>
+          <t>04/11/2025</t>
         </is>
       </c>
       <c r="F31" s="7" t="inlineStr">
@@ -2105,16 +2105,16 @@
       </c>
       <c r="K31" s="6"/>
       <c r="L31" s="13" t="n">
-        <v>462963.0</v>
+        <v>740741.0</v>
       </c>
       <c r="M31" s="13" t="n">
-        <v>37037.0</v>
+        <v>59259.0</v>
       </c>
       <c r="N31" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O31" s="13" t="n">
-        <v>500000.0</v>
+        <v>800000.0</v>
       </c>
       <c r="P31" s="6" t="inlineStr">
         <is>
@@ -2143,12 +2143,12 @@
       </c>
       <c r="D32" s="7" t="inlineStr">
         <is>
-          <t>270810</t>
+          <t>267298</t>
         </is>
       </c>
       <c r="E32" s="7" t="inlineStr">
         <is>
-          <t>11/11/2025</t>
+          <t>07/11/2025</t>
         </is>
       </c>
       <c r="F32" s="7" t="inlineStr">
@@ -2216,12 +2216,12 @@
       </c>
       <c r="D33" s="7" t="inlineStr">
         <is>
-          <t>274708</t>
+          <t>269619</t>
         </is>
       </c>
       <c r="E33" s="7" t="inlineStr">
         <is>
-          <t>15/11/2025</t>
+          <t>10/11/2025</t>
         </is>
       </c>
       <c r="F33" s="7" t="inlineStr">
@@ -2251,16 +2251,16 @@
       </c>
       <c r="K33" s="6"/>
       <c r="L33" s="13" t="n">
-        <v>740741.0</v>
+        <v>462963.0</v>
       </c>
       <c r="M33" s="13" t="n">
-        <v>59259.0</v>
+        <v>37037.0</v>
       </c>
       <c r="N33" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O33" s="13" t="n">
-        <v>800000.0</v>
+        <v>500000.0</v>
       </c>
       <c r="P33" s="6" t="inlineStr">
         <is>
@@ -2289,12 +2289,12 @@
       </c>
       <c r="D34" s="7" t="inlineStr">
         <is>
-          <t>278331</t>
+          <t>270810</t>
         </is>
       </c>
       <c r="E34" s="7" t="inlineStr">
         <is>
-          <t>18/11/2025</t>
+          <t>11/11/2025</t>
         </is>
       </c>
       <c r="F34" s="7" t="inlineStr">
@@ -2341,6 +2341,653 @@
         </is>
       </c>
       <c r="Q34" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="n">
+        <v>29.0</v>
+      </c>
+      <c r="B35" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C35" s="6" t="inlineStr">
+        <is>
+          <t>C25MDO</t>
+        </is>
+      </c>
+      <c r="D35" s="7" t="inlineStr">
+        <is>
+          <t>274708</t>
+        </is>
+      </c>
+      <c r="E35" s="7" t="inlineStr">
+        <is>
+          <t>15/11/2025</t>
+        </is>
+      </c>
+      <c r="F35" s="7" t="inlineStr">
+        <is>
+          <t>3502397072</t>
+        </is>
+      </c>
+      <c r="G35" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH XĂNG DẦU VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H35" s="6" t="inlineStr">
+        <is>
+          <t>Số 510 Cách Mạng Tháng Tám, Phường Bà Rịa, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I35" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J35" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="K35" s="6"/>
+      <c r="L35" s="13" t="n">
+        <v>740741.0</v>
+      </c>
+      <c r="M35" s="13" t="n">
+        <v>59259.0</v>
+      </c>
+      <c r="N35" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O35" s="13" t="n">
+        <v>800000.0</v>
+      </c>
+      <c r="P35" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q35" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="n">
+        <v>30.0</v>
+      </c>
+      <c r="B36" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C36" s="6" t="inlineStr">
+        <is>
+          <t>C25MDO</t>
+        </is>
+      </c>
+      <c r="D36" s="7" t="inlineStr">
+        <is>
+          <t>278331</t>
+        </is>
+      </c>
+      <c r="E36" s="7" t="inlineStr">
+        <is>
+          <t>18/11/2025</t>
+        </is>
+      </c>
+      <c r="F36" s="7" t="inlineStr">
+        <is>
+          <t>3502397072</t>
+        </is>
+      </c>
+      <c r="G36" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH XĂNG DẦU VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H36" s="6" t="inlineStr">
+        <is>
+          <t>Số 510 Cách Mạng Tháng Tám, Phường Bà Rịa, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I36" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J36" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="K36" s="6"/>
+      <c r="L36" s="13" t="n">
+        <v>740741.0</v>
+      </c>
+      <c r="M36" s="13" t="n">
+        <v>59259.0</v>
+      </c>
+      <c r="N36" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O36" s="13" t="n">
+        <v>800000.0</v>
+      </c>
+      <c r="P36" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q36" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="n">
+        <v>31.0</v>
+      </c>
+      <c r="B37" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C37" s="6" t="inlineStr">
+        <is>
+          <t>C25MDO</t>
+        </is>
+      </c>
+      <c r="D37" s="7" t="inlineStr">
+        <is>
+          <t>281364</t>
+        </is>
+      </c>
+      <c r="E37" s="7" t="inlineStr">
+        <is>
+          <t>22/11/2025</t>
+        </is>
+      </c>
+      <c r="F37" s="7" t="inlineStr">
+        <is>
+          <t>3502397072</t>
+        </is>
+      </c>
+      <c r="G37" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH XĂNG DẦU VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H37" s="6" t="inlineStr">
+        <is>
+          <t>Số 510 Cách Mạng Tháng Tám, Phường Bà Rịa, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I37" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J37" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="K37" s="6"/>
+      <c r="L37" s="13" t="n">
+        <v>740741.0</v>
+      </c>
+      <c r="M37" s="13" t="n">
+        <v>59259.0</v>
+      </c>
+      <c r="N37" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O37" s="13" t="n">
+        <v>800000.0</v>
+      </c>
+      <c r="P37" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q37" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="n">
+        <v>32.0</v>
+      </c>
+      <c r="B38" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C38" s="6" t="inlineStr">
+        <is>
+          <t>C25MDO</t>
+        </is>
+      </c>
+      <c r="D38" s="7" t="inlineStr">
+        <is>
+          <t>284965</t>
+        </is>
+      </c>
+      <c r="E38" s="7" t="inlineStr">
+        <is>
+          <t>25/11/2025</t>
+        </is>
+      </c>
+      <c r="F38" s="7" t="inlineStr">
+        <is>
+          <t>3502397072</t>
+        </is>
+      </c>
+      <c r="G38" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH XĂNG DẦU VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H38" s="6" t="inlineStr">
+        <is>
+          <t>Số 510 Cách Mạng Tháng Tám, Phường Bà Rịa, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I38" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J38" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="K38" s="6"/>
+      <c r="L38" s="13" t="n">
+        <v>740741.0</v>
+      </c>
+      <c r="M38" s="13" t="n">
+        <v>59259.0</v>
+      </c>
+      <c r="N38" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O38" s="13" t="n">
+        <v>800000.0</v>
+      </c>
+      <c r="P38" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q38" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="n">
+        <v>33.0</v>
+      </c>
+      <c r="B39" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C39" s="6" t="inlineStr">
+        <is>
+          <t>C25MMC</t>
+        </is>
+      </c>
+      <c r="D39" s="7" t="inlineStr">
+        <is>
+          <t>208589</t>
+        </is>
+      </c>
+      <c r="E39" s="7" t="inlineStr">
+        <is>
+          <t>27/11/2025</t>
+        </is>
+      </c>
+      <c r="F39" s="7" t="inlineStr">
+        <is>
+          <t>3502545901</t>
+        </is>
+      </c>
+      <c r="G39" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH MINH CHÂU MART</t>
+        </is>
+      </c>
+      <c r="H39" s="6" t="inlineStr">
+        <is>
+          <t>Số 63 Đội Cấn, Phường Tam Thắng, Thành phố Hồ Chí Minh, Việt Nam.</t>
+        </is>
+      </c>
+      <c r="I39" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J39" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="K39" s="6"/>
+      <c r="L39" s="13" t="n">
+        <v>1577777.78</v>
+      </c>
+      <c r="M39" s="13" t="n">
+        <v>126222.22</v>
+      </c>
+      <c r="N39" s="13"/>
+      <c r="O39" s="13" t="n">
+        <v>1704000.0</v>
+      </c>
+      <c r="P39" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q39" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="n">
+        <v>34.0</v>
+      </c>
+      <c r="B40" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C40" s="6" t="inlineStr">
+        <is>
+          <t>C25MMC</t>
+        </is>
+      </c>
+      <c r="D40" s="7" t="inlineStr">
+        <is>
+          <t>208590</t>
+        </is>
+      </c>
+      <c r="E40" s="7" t="inlineStr">
+        <is>
+          <t>27/11/2025</t>
+        </is>
+      </c>
+      <c r="F40" s="7" t="inlineStr">
+        <is>
+          <t>3502545901</t>
+        </is>
+      </c>
+      <c r="G40" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH MINH CHÂU MART</t>
+        </is>
+      </c>
+      <c r="H40" s="6" t="inlineStr">
+        <is>
+          <t>Số 63 Đội Cấn, Phường Tam Thắng, Thành phố Hồ Chí Minh, Việt Nam.</t>
+        </is>
+      </c>
+      <c r="I40" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J40" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="K40" s="6"/>
+      <c r="L40" s="13" t="n">
+        <v>659259.26</v>
+      </c>
+      <c r="M40" s="13" t="n">
+        <v>52740.74</v>
+      </c>
+      <c r="N40" s="13"/>
+      <c r="O40" s="13" t="n">
+        <v>712000.0</v>
+      </c>
+      <c r="P40" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q40" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="n">
+        <v>35.0</v>
+      </c>
+      <c r="B41" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C41" s="6" t="inlineStr">
+        <is>
+          <t>C25MMC</t>
+        </is>
+      </c>
+      <c r="D41" s="7" t="inlineStr">
+        <is>
+          <t>208591</t>
+        </is>
+      </c>
+      <c r="E41" s="7" t="inlineStr">
+        <is>
+          <t>27/11/2025</t>
+        </is>
+      </c>
+      <c r="F41" s="7" t="inlineStr">
+        <is>
+          <t>3502545901</t>
+        </is>
+      </c>
+      <c r="G41" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH MINH CHÂU MART</t>
+        </is>
+      </c>
+      <c r="H41" s="6" t="inlineStr">
+        <is>
+          <t>Số 63 Đội Cấn, Phường Tam Thắng, Thành phố Hồ Chí Minh, Việt Nam.</t>
+        </is>
+      </c>
+      <c r="I41" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J41" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="K41" s="6"/>
+      <c r="L41" s="13" t="n">
+        <v>222222.22</v>
+      </c>
+      <c r="M41" s="13" t="n">
+        <v>17777.78</v>
+      </c>
+      <c r="N41" s="13"/>
+      <c r="O41" s="13" t="n">
+        <v>240000.0</v>
+      </c>
+      <c r="P41" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q41" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="n">
+        <v>36.0</v>
+      </c>
+      <c r="B42" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C42" s="6" t="inlineStr">
+        <is>
+          <t>C25MMC</t>
+        </is>
+      </c>
+      <c r="D42" s="7" t="inlineStr">
+        <is>
+          <t>208592</t>
+        </is>
+      </c>
+      <c r="E42" s="7" t="inlineStr">
+        <is>
+          <t>27/11/2025</t>
+        </is>
+      </c>
+      <c r="F42" s="7" t="inlineStr">
+        <is>
+          <t>3502545901</t>
+        </is>
+      </c>
+      <c r="G42" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH MINH CHÂU MART</t>
+        </is>
+      </c>
+      <c r="H42" s="6" t="inlineStr">
+        <is>
+          <t>Số 63 Đội Cấn, Phường Tam Thắng, Thành phố Hồ Chí Minh, Việt Nam.</t>
+        </is>
+      </c>
+      <c r="I42" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J42" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="K42" s="6"/>
+      <c r="L42" s="13" t="n">
+        <v>337962.96</v>
+      </c>
+      <c r="M42" s="13" t="n">
+        <v>27037.04</v>
+      </c>
+      <c r="N42" s="13"/>
+      <c r="O42" s="13" t="n">
+        <v>365000.0</v>
+      </c>
+      <c r="P42" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q42" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="n">
+        <v>37.0</v>
+      </c>
+      <c r="B43" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C43" s="6" t="inlineStr">
+        <is>
+          <t>C25MMC</t>
+        </is>
+      </c>
+      <c r="D43" s="7" t="inlineStr">
+        <is>
+          <t>208593</t>
+        </is>
+      </c>
+      <c r="E43" s="7" t="inlineStr">
+        <is>
+          <t>27/11/2025</t>
+        </is>
+      </c>
+      <c r="F43" s="7" t="inlineStr">
+        <is>
+          <t>3502545901</t>
+        </is>
+      </c>
+      <c r="G43" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH MINH CHÂU MART</t>
+        </is>
+      </c>
+      <c r="H43" s="6" t="inlineStr">
+        <is>
+          <t>Số 63 Đội Cấn, Phường Tam Thắng, Thành phố Hồ Chí Minh, Việt Nam.</t>
+        </is>
+      </c>
+      <c r="I43" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J43" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="K43" s="6"/>
+      <c r="L43" s="13" t="n">
+        <v>243518.52</v>
+      </c>
+      <c r="M43" s="13" t="n">
+        <v>19481.48</v>
+      </c>
+      <c r="N43" s="13"/>
+      <c r="O43" s="13" t="n">
+        <v>263000.0</v>
+      </c>
+      <c r="P43" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q43" s="6" t="inlineStr">
         <is>
           <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
         </is>
